--- a/data/user.xlsx
+++ b/data/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73AAB4D-91AF-4003-9FB3-D6AC0E9FAB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4AAC71-732F-4FC2-BE02-114EC1299CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -1497,7 +1497,9 @@
       <c r="C23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>65</v>
       </c>
@@ -1527,7 +1529,9 @@
       <c r="C24" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>66</v>
       </c>
@@ -1557,7 +1561,9 @@
       <c r="C25" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
@@ -1587,7 +1593,9 @@
       <c r="C26" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>68</v>
       </c>
@@ -1617,7 +1625,9 @@
       <c r="C27" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>69</v>
       </c>
@@ -1647,7 +1657,9 @@
       <c r="C28" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
       </c>
@@ -1677,7 +1689,9 @@
       <c r="C29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
       </c>
@@ -1707,7 +1721,9 @@
       <c r="C30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
       </c>
@@ -1737,7 +1753,9 @@
       <c r="C31" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>73</v>
       </c>
@@ -1767,7 +1785,9 @@
       <c r="C32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>74</v>
       </c>
@@ -1797,7 +1817,9 @@
       <c r="C33" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>75</v>
       </c>
@@ -1827,7 +1849,9 @@
       <c r="C34" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>76</v>
       </c>
@@ -1857,7 +1881,9 @@
       <c r="C35" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="4"/>
+      <c r="D35" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E35" s="2" t="s">
         <v>77</v>
       </c>
@@ -1887,7 +1913,9 @@
       <c r="C36" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>78</v>
       </c>
@@ -1917,7 +1945,9 @@
       <c r="C37" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="4"/>
+      <c r="D37" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>79</v>
       </c>
@@ -1947,7 +1977,9 @@
       <c r="C38" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="4"/>
+      <c r="D38" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>80</v>
       </c>
@@ -1977,7 +2009,9 @@
       <c r="C39" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="D39" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>81</v>
       </c>
@@ -2007,7 +2041,9 @@
       <c r="C40" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>82</v>
       </c>
@@ -2037,7 +2073,9 @@
       <c r="C41" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="4"/>
+      <c r="D41" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>83</v>
       </c>

--- a/data/user.xlsx
+++ b/data/user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Training\Gathering_Island\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4AAC71-732F-4FC2-BE02-114EC1299CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EB9848-9D47-4D90-A86D-A293B4B25B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22875" yWindow="5190" windowWidth="18585" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="108">
   <si>
     <t>id</t>
   </si>
@@ -373,6 +373,14 @@
   </si>
   <si>
     <t>2025-11-01 17:53:46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meri@test.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meri</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2096,13 +2104,30 @@
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="3"/>
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
